--- a/地图表格/level9.xlsx
+++ b/地图表格/level9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\52724\SIMGame\SIMGame\地图表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F2C013-7DF6-470D-AB3E-C5A82F19F533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3E3A08-DE96-46DB-8FD8-E83F8F5E880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E3CA8487-19F0-4030-A3BB-EA17CE43E315}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>出生点</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,10 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>反派出生点：反派初始从这里开始移动，移速待定，碰撞体积、立绘大小、重力等属性同主角，初始固定向左移动，第一次坠落时反向，遇到种子时将其摧毁，被摧毁的种子不能再萌发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>陷阱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,15 +88,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>推动机关：玩家可以推动滑钮左右移动，被控制的可动砖块随之移动，类似冰火人；被控制的可动砖块移动范围为初始位置（可动砖块2）＋右侧（可动位置2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可动位置2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>反光镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反光镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推动机关3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推动机关2：玩家可以推动滑钮左右移动，被控制的可动砖块随之移动，类似冰火人；被控制的可动砖块移动范围为初始位置（可动砖块2）＋右侧（可动位置2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>折射镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推动机关3：类似推动机关2，但是控制折射镜方向，可控制通过折射镜的光线方向左右旋转，本关所有的折射镜都和该推动机关联动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反派出生点：反派初始从这里开始移动，移速待定，碰撞体积、立绘大小、重力等属性同主角，初始固定向左移动，遇到种子时将其摧毁，被摧毁的种子不能再萌发，每次撞墙或坠落后反向，不能推动箱子，但是触碰主角时主角死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关5：需要当前萌发值=max才会显示出来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该颜色砖块为隐形砖块，不可见，其他属性均同墙体，可以阻挡光线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -125,7 +161,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,6 +219,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -201,7 +267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -211,38 +277,59 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,24 +654,22 @@
     </row>
     <row r="2" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="AR2" s="3" t="s">
+      <c r="AR2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AS2" s="3"/>
+      <c r="AS2" s="10"/>
       <c r="AX2" s="1"/>
     </row>
     <row r="3" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
       <c r="AX3" s="1"/>
     </row>
     <row r="4" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -634,92 +719,90 @@
     <row r="5" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="AX5" s="1"/>
-      <c r="BB5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC5" s="4"/>
-      <c r="BD5" s="4"/>
-      <c r="BE5" s="4"/>
-      <c r="BF5" s="4"/>
-      <c r="BG5" s="4"/>
+      <c r="BB5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC5" s="6"/>
+      <c r="BD5" s="6"/>
+      <c r="BE5" s="6"/>
+      <c r="BF5" s="6"/>
+      <c r="BG5" s="6"/>
     </row>
     <row r="6" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="AX6" s="1"/>
-      <c r="BB6" s="4"/>
-      <c r="BC6" s="4"/>
-      <c r="BD6" s="4"/>
-      <c r="BE6" s="4"/>
-      <c r="BF6" s="4"/>
-      <c r="BG6" s="4"/>
+      <c r="BB6" s="6"/>
+      <c r="BC6" s="6"/>
+      <c r="BD6" s="6"/>
+      <c r="BE6" s="6"/>
+      <c r="BF6" s="6"/>
+      <c r="BG6" s="6"/>
     </row>
     <row r="7" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AX7" s="1"/>
-      <c r="BB7" s="4"/>
-      <c r="BC7" s="4"/>
-      <c r="BD7" s="4"/>
-      <c r="BE7" s="4"/>
-      <c r="BF7" s="4"/>
-      <c r="BG7" s="4"/>
+      <c r="BB7" s="6"/>
+      <c r="BC7" s="6"/>
+      <c r="BD7" s="6"/>
+      <c r="BE7" s="6"/>
+      <c r="BF7" s="6"/>
+      <c r="BG7" s="6"/>
     </row>
     <row r="8" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="6"/>
-      <c r="AM8" s="6"/>
-      <c r="AN8" s="6"/>
-      <c r="AO8" s="6"/>
-      <c r="AP8" s="6"/>
-      <c r="AQ8" s="6"/>
-      <c r="AR8" s="5"/>
-      <c r="AS8" s="5"/>
-      <c r="AT8" s="6" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AT8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AU8" s="6"/>
-      <c r="AV8" s="6"/>
-      <c r="AW8" s="6"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
       <c r="AX8" s="1"/>
     </row>
     <row r="9" spans="1:59" x14ac:dyDescent="0.3">
@@ -733,38 +816,58 @@
       <c r="Q10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AX10" s="1"/>
-      <c r="BB10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="BC10" s="4"/>
-      <c r="BD10" s="4"/>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
-      <c r="BG10" s="4"/>
+      <c r="BB10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BC10" s="6"/>
+      <c r="BD10" s="6"/>
+      <c r="BE10" s="6"/>
+      <c r="BF10" s="6"/>
+      <c r="BG10" s="6"/>
     </row>
     <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AX11" s="1"/>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="4"/>
-      <c r="BD11" s="4"/>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
-      <c r="BG11" s="4"/>
+      <c r="BB11" s="6"/>
+      <c r="BC11" s="6"/>
+      <c r="BD11" s="6"/>
+      <c r="BE11" s="6"/>
+      <c r="BF11" s="6"/>
+      <c r="BG11" s="6"/>
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="Q12" s="1"/>
+      <c r="T12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="AH12" s="1"/>
       <c r="AX12" s="1"/>
-      <c r="BB12" s="4"/>
-      <c r="BC12" s="4"/>
-      <c r="BD12" s="4"/>
-      <c r="BE12" s="4"/>
-      <c r="BF12" s="4"/>
-      <c r="BG12" s="4"/>
+      <c r="BB12" s="6"/>
+      <c r="BC12" s="6"/>
+      <c r="BD12" s="6"/>
+      <c r="BE12" s="6"/>
+      <c r="BF12" s="6"/>
+      <c r="BG12" s="6"/>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -774,211 +877,383 @@
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
+      <c r="H14" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="Q14" s="1"/>
       <c r="AH14" s="1"/>
+      <c r="AW14" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="AX14" s="1"/>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="Q15" s="1"/>
+      <c r="T15" s="13"/>
       <c r="AH15" s="1"/>
       <c r="AX15" s="1"/>
-      <c r="BB15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="BC15" s="4"/>
-      <c r="BD15" s="4"/>
-      <c r="BE15" s="4"/>
-      <c r="BF15" s="4"/>
-      <c r="BG15" s="4"/>
+      <c r="BB15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="BC15" s="6"/>
+      <c r="BD15" s="6"/>
+      <c r="BE15" s="6"/>
+      <c r="BF15" s="6"/>
+      <c r="BG15" s="6"/>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="Q16" s="1"/>
+      <c r="T16" s="19"/>
       <c r="AH16" s="1"/>
       <c r="AX16" s="1"/>
-      <c r="BB16" s="4"/>
-      <c r="BC16" s="4"/>
-      <c r="BD16" s="4"/>
-      <c r="BE16" s="4"/>
-      <c r="BF16" s="4"/>
-      <c r="BG16" s="4"/>
-    </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB16" s="6"/>
+      <c r="BC16" s="6"/>
+      <c r="BD16" s="6"/>
+      <c r="BE16" s="6"/>
+      <c r="BF16" s="6"/>
+      <c r="BG16" s="6"/>
+    </row>
+    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="Q17" s="1"/>
+      <c r="T17" s="19"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
       <c r="AH17" s="1"/>
       <c r="AX17" s="1"/>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="Q18" s="1"/>
+      <c r="T18" s="19"/>
       <c r="AH18" s="1"/>
       <c r="AX18" s="1"/>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="Q19" s="1"/>
+      <c r="T19" s="19"/>
       <c r="AH19" s="1"/>
       <c r="AX19" s="1"/>
-    </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="BC19" s="6"/>
+      <c r="BD19" s="6"/>
+      <c r="BE19" s="6"/>
+      <c r="BF19" s="6"/>
+      <c r="BG19" s="6"/>
+    </row>
+    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="Q20" s="1"/>
+      <c r="T20" s="19"/>
+      <c r="X20" s="13"/>
       <c r="AH20" s="1"/>
+      <c r="AR20" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="AX20" s="1"/>
-    </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB20" s="6"/>
+      <c r="BC20" s="6"/>
+      <c r="BD20" s="6"/>
+      <c r="BE20" s="6"/>
+      <c r="BF20" s="6"/>
+      <c r="BG20" s="6"/>
+    </row>
+    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="Q21" s="1"/>
+      <c r="T21" s="19"/>
+      <c r="V21" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="AH21" s="1"/>
+      <c r="AI21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+      <c r="AP21" s="19"/>
+      <c r="AQ21" s="19"/>
+      <c r="AR21" s="19"/>
+      <c r="AS21" s="19"/>
+      <c r="AT21" s="19"/>
+      <c r="AU21" s="19"/>
+      <c r="AV21" s="19"/>
+      <c r="AW21" s="19"/>
       <c r="AX21" s="1"/>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
+      <c r="F22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="19"/>
       <c r="Q22" s="1"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
       <c r="AH22" s="1"/>
+      <c r="AU22" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="AX22" s="1"/>
-    </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC22" s="6"/>
+      <c r="BD22" s="6"/>
+      <c r="BE22" s="6"/>
+      <c r="BF22" s="6"/>
+      <c r="BG22" s="6"/>
+    </row>
+    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
+      <c r="J23" s="19"/>
       <c r="Q23" s="1"/>
+      <c r="T23" s="19"/>
       <c r="AH23" s="1"/>
       <c r="AX23" s="1"/>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB23" s="6"/>
+      <c r="BC23" s="6"/>
+      <c r="BD23" s="6"/>
+      <c r="BE23" s="6"/>
+      <c r="BF23" s="6"/>
+      <c r="BG23" s="6"/>
+    </row>
+    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
+      <c r="J24" s="19"/>
       <c r="Q24" s="1"/>
+      <c r="T24" s="19"/>
       <c r="AH24" s="1"/>
       <c r="AX24" s="1"/>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
+      <c r="F25" s="19"/>
       <c r="Q25" s="1"/>
+      <c r="T25" s="19"/>
       <c r="AH25" s="1"/>
       <c r="AX25" s="1"/>
-    </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB25" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC25" s="20"/>
+      <c r="BD25" s="20"/>
+      <c r="BE25" s="20"/>
+      <c r="BF25" s="20"/>
+      <c r="BG25" s="20"/>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
+      <c r="F26" s="19"/>
       <c r="Q26" s="1"/>
+      <c r="T26" s="19"/>
       <c r="AH26" s="1"/>
       <c r="AX26" s="1"/>
-    </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="BB26" s="20"/>
+      <c r="BC26" s="20"/>
+      <c r="BD26" s="20"/>
+      <c r="BE26" s="20"/>
+      <c r="BF26" s="20"/>
+      <c r="BG26" s="20"/>
+    </row>
+    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
+      <c r="F27" s="19"/>
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="Q27" s="1"/>
+      <c r="T27" s="19"/>
       <c r="AH27" s="1"/>
+      <c r="AK27" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="AX27" s="1"/>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
       <c r="Q28" s="1"/>
+      <c r="T28" s="19"/>
+      <c r="W28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB28" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="AH28" s="1"/>
+      <c r="AI28" s="19"/>
+      <c r="AJ28" s="19"/>
+      <c r="AK28" s="19"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="19"/>
+      <c r="AP28" s="19"/>
+      <c r="AQ28" s="19"/>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="19"/>
+      <c r="AT28" s="19"/>
+      <c r="AW28" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="AX28" s="1"/>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="Q29" s="1"/>
+      <c r="T29" s="19"/>
       <c r="AH29" s="1"/>
       <c r="AX29" s="1"/>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="Q30" s="1"/>
+      <c r="T30" s="19"/>
       <c r="AH30" s="1"/>
       <c r="AX30" s="1"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="Q31" s="1"/>
+      <c r="T31" s="19"/>
       <c r="AH31" s="1"/>
       <c r="AX31" s="1"/>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="Q32" s="1"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="19"/>
+      <c r="AA32" s="19"/>
+      <c r="AB32" s="19"/>
+      <c r="AC32" s="19"/>
+      <c r="AD32" s="19"/>
+      <c r="AE32" s="19"/>
+      <c r="AF32" s="19"/>
+      <c r="AG32" s="19"/>
       <c r="AH32" s="1"/>
       <c r="AX32" s="1"/>
     </row>
     <row r="33" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="AH33" s="1"/>
+      <c r="Q33" s="13"/>
+      <c r="AH33" s="13"/>
       <c r="AX33" s="1"/>
     </row>
     <row r="34" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="E34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="Q34" s="1"/>
-      <c r="AH34" s="1"/>
+      <c r="E34" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="Q34" s="13"/>
+      <c r="AH34" s="13"/>
       <c r="AX34" s="1"/>
     </row>
     <row r="35" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="Q35" s="1"/>
-      <c r="AH35" s="1"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="Q35" s="13"/>
+      <c r="AH35" s="13"/>
       <c r="AX35" s="1"/>
     </row>
     <row r="36" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="C36" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
-      <c r="AC36" s="12"/>
-      <c r="AD36" s="12"/>
-      <c r="AE36" s="12"/>
-      <c r="AF36" s="12"/>
-      <c r="AG36" s="12"/>
-      <c r="AH36" s="12"/>
-      <c r="AI36" s="12"/>
-      <c r="AJ36" s="12"/>
-      <c r="AK36" s="12"/>
-      <c r="AL36" s="12"/>
-      <c r="AM36" s="12"/>
-      <c r="AN36" s="12"/>
-      <c r="AO36" s="12"/>
-      <c r="AP36" s="12"/>
-      <c r="AQ36" s="12"/>
-      <c r="AR36" s="12"/>
-      <c r="AS36" s="12"/>
-      <c r="AT36" s="12"/>
-      <c r="AU36" s="12"/>
-      <c r="AV36" s="12"/>
+      <c r="C36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="9"/>
+      <c r="AH36" s="9"/>
+      <c r="AI36" s="9"/>
+      <c r="AJ36" s="9"/>
+      <c r="AK36" s="9"/>
+      <c r="AL36" s="9"/>
+      <c r="AM36" s="9"/>
+      <c r="AN36" s="9"/>
+      <c r="AO36" s="9"/>
+      <c r="AP36" s="9"/>
+      <c r="AQ36" s="9"/>
+      <c r="AR36" s="9"/>
+      <c r="AS36" s="9"/>
+      <c r="AT36" s="9"/>
+      <c r="AU36" s="9"/>
+      <c r="AV36" s="9"/>
       <c r="AX36" s="1"/>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.3">
@@ -999,17 +1274,24 @@
     </row>
     <row r="41" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="AS41" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AT41" s="11"/>
-      <c r="AU41" s="11"/>
-      <c r="AV41" s="11"/>
-      <c r="AW41" s="11"/>
+      <c r="AS41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT41" s="8"/>
+      <c r="AU41" s="8"/>
+      <c r="AV41" s="8"/>
+      <c r="AW41" s="8"/>
       <c r="AX41" s="1"/>
     </row>
     <row r="42" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
+      <c r="B42" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
       <c r="AX42" s="1"/>
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.3">
@@ -1023,15 +1305,18 @@
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
       <c r="R44" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S44" s="7"/>
-      <c r="AM44" s="5"/>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
-      <c r="AQ44" s="5"/>
       <c r="AX44" s="1"/>
     </row>
     <row r="45" spans="1:50" x14ac:dyDescent="0.3">
@@ -1044,8 +1329,8 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
-      <c r="AI45" s="8" t="s">
-        <v>6</v>
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AX45" s="1"/>
     </row>
@@ -1053,7 +1338,6 @@
       <c r="A46" s="1"/>
       <c r="O46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="AF46" s="5"/>
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
@@ -1064,53 +1348,53 @@
     <row r="47" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="O47" s="1"/>
-      <c r="V47" s="10" t="s">
-        <v>8</v>
+      <c r="V47" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="AX47" s="1"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="10"/>
       <c r="O48" s="1"/>
-      <c r="R48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="S48" s="3"/>
-      <c r="V48" s="10"/>
+      <c r="R48" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S48" s="10"/>
+      <c r="V48" s="11"/>
       <c r="AX48" s="1"/>
     </row>
     <row r="49" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
       <c r="G49" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
-      <c r="M49" s="8" t="s">
-        <v>6</v>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="1"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="V49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="V49" s="11"/>
       <c r="AA49" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB49" s="7"/>
       <c r="AC49" s="7"/>
       <c r="AD49" s="7"/>
-      <c r="AN49" s="9" t="s">
-        <v>12</v>
+      <c r="AN49" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="AQ49" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR49" s="7"/>
       <c r="AS49" s="7"/>
@@ -1171,7 +1455,16 @@
       <c r="AX50" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
+    <mergeCell ref="AR2:AS3"/>
+    <mergeCell ref="R48:S49"/>
+    <mergeCell ref="V47:V49"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="E34:F35"/>
+    <mergeCell ref="C48:D49"/>
+    <mergeCell ref="B8:AQ8"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="BB5:BG7"/>
     <mergeCell ref="AA49:AD49"/>
     <mergeCell ref="R44:S44"/>
@@ -1179,16 +1472,11 @@
     <mergeCell ref="BB15:BG16"/>
     <mergeCell ref="AS41:AW41"/>
     <mergeCell ref="I36:AV36"/>
-    <mergeCell ref="AR2:AS3"/>
-    <mergeCell ref="R48:S49"/>
-    <mergeCell ref="V47:V49"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="E34:F35"/>
-    <mergeCell ref="C48:D49"/>
-    <mergeCell ref="B8:AQ8"/>
     <mergeCell ref="AT8:AW8"/>
-    <mergeCell ref="G49:J49"/>
     <mergeCell ref="BB10:BG12"/>
+    <mergeCell ref="BB19:BG20"/>
+    <mergeCell ref="BB22:BG23"/>
+    <mergeCell ref="BB25:BG26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
